--- a/feedback_forms/001_store_features_evaluation_form--feedback_forms.xlsx
+++ b/feedback_forms/001_store_features_evaluation_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,20 +515,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_1</t>
+          <t>overall_impression</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Store Features Evaluation Form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your overall impression of the store's appearance?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide your honest feedback on the store's appearance.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,20 +542,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_2</t>
+          <t>product_variety</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>store features</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>How would you rate the store's product variety?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Rate the variety of products available at the store.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -561,161 +569,189 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_3</t>
+          <t>customer_service</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>store features evaluation form</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>How would you rate the store's customer service?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Rate the helpfulness and friendliness of the store's staff.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_4</t>
+          <t>favorite_product</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>store features evaluation form</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What is your favorite product or feature at the store?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please specify your favorite product or feature.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_5</t>
+          <t>website_navigation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>store features</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>How easy was it to navigate the store's website?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Rate the ease of navigation on the store's website.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_6</t>
+          <t>product_quality</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>store features</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How would you rate the store's product quality?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Rate the quality of products available at the store.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_7</t>
+          <t>prices</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>store features evaluation form</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>How would you rate the store's prices?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Rate the store's prices in comparison to other stores.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_8</t>
+          <t>store_environment</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>store features</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>How would you rate the store's environment?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Rate the store's cleanliness and comfort.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_9</t>
+          <t>checkout_process</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>store features</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>How would you rate the store's checkout process?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rate the efficiency of the checkout process.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,38 +763,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_10</t>
+          <t>return_to_store</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>store features</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Would you return to this store in the future?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please indicate your likelihood of returning to the store.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_11</t>
+          <t>like_most_about_store</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>store features evaluation form</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What did you like most about the store?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Specify the feature or product you liked most.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,322 +812,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_12</t>
+          <t>store_suggestions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>store features</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What suggestions do you have for the store's improvement?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Provide feedback to help the store improve.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>store_features_evaluation_form_page_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>store features</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>store_features_evaluation_form_page_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>store features evaluation form</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>store_features_evaluation_form_page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>store features</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>store_features_evaluation_form_page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>store features</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>store_features_evaluation_form_page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>store features evaluation form</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>store_features_evaluation_form_page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>store features evaluation form</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>store_features_evaluation_form_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>store features</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>store_features_evaluation_form_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>store features</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>store_features_evaluation_form_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>store features</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>store_features_evaluation_form_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>store features evaluation form</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>store_features_evaluation_form_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>store features</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>store_features_evaluation_form_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>store features</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>store_features_evaluation_form_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>store features evaluation form</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1098,10 +847,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +875,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_3_choices</t>
+          <t>product_variety_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,58 +892,58 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_3_choices</t>
+          <t>product_variety_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>poor_(5/10)</t>
+          <t>good_(7/10)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Poor (5/10)</t>
+          <t>Good (7/10)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_3_choices</t>
+          <t>product_variety_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>good_(7/10)</t>
+          <t>fair_(6/10)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Good (7/10)</t>
+          <t>Fair (6/10)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_3_choices</t>
+          <t>product_variety_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fair_(6/10)</t>
+          <t>poor_(5/10)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fair (6/10)</t>
+          <t>Poor (5/10)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_4_choices</t>
+          <t>customer_service_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,58 +960,58 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_4_choices</t>
+          <t>customer_service_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>poor_(5/10)</t>
+          <t>good_(7/10)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poor (5/10)</t>
+          <t>Good (7/10)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_4_choices</t>
+          <t>customer_service_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>good_(7/10)</t>
+          <t>fair_(6/10)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Good (7/10)</t>
+          <t>Fair (6/10)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_4_choices</t>
+          <t>customer_service_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fair_(6/10)</t>
+          <t>poor_(5/10)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fair (6/10)</t>
+          <t>Poor (5/10)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_17_choices</t>
+          <t>website_navigation_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,41 +1028,41 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_17_choices</t>
+          <t>website_navigation_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>poor_(5/10)</t>
+          <t>good_(7/10)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poor (5/10)</t>
+          <t>Good (7/10)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_18_choices</t>
+          <t>website_navigation_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>excellent_(9/10)</t>
+          <t>fair_(6/10)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Excellent (9/10)</t>
+          <t>Fair (6/10)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>store_features_evaluation_form_page_18_choices</t>
+          <t>website_navigation_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1322,6 +1071,278 @@
         </is>
       </c>
       <c r="C13" t="inlineStr">
+        <is>
+          <t>Poor (5/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>product_quality_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>excellent_(9/10)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Excellent (9/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>product_quality_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>good_(7/10)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Good (7/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>product_quality_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>fair_(6/10)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Fair (6/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>product_quality_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>poor_(5/10)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Poor (5/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>prices_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>excellent_(9/10)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Excellent (9/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>prices_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>good_(7/10)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Good (7/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>prices_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>fair_(6/10)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Fair (6/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>prices_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>poor_(5/10)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Poor (5/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>store_environment_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>excellent_(9/10)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Excellent (9/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>store_environment_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>good_(7/10)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Good (7/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>store_environment_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>fair_(6/10)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Fair (6/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>store_environment_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>poor_(5/10)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Poor (5/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>checkout_process_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>excellent_(9/10)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Excellent (9/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>checkout_process_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>good_(7/10)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Good (7/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>checkout_process_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>fair_(6/10)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Fair (6/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>checkout_process_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>poor_(5/10)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>Poor (5/10)</t>
         </is>
